--- a/results/preperation.xlsx
+++ b/results/preperation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t xml:space="preserve">Generator </t>
   </si>
@@ -80,6 +80,9 @@
   <si>
     <t>Desis</t>
   </si>
+  <si>
+    <t>heighest</t>
+  </si>
 </sst>
 </file>
 
@@ -120,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -129,6 +132,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -186,7 +190,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -449,7 +452,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -814,7 +816,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -964,7 +965,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1294,7 +1294,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1419,7 +1418,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1749,7 +1747,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1899,7 +1896,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2199,7 +2195,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6122,15 +6117,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>3175</xdr:rowOff>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>48895</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>168275</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>130810</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>31115</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6440,18 +6435,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H86"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6461,7 +6456,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6469,7 +6464,7 @@
         <v>1354279</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6480,7 +6475,7 @@
         <v>1176458</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6488,7 +6483,7 @@
         <v>2462051</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6496,7 +6491,7 @@
         <v>2769908</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6504,7 +6499,7 @@
         <v>3114585</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6512,7 +6507,7 @@
         <v>3468657</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6520,7 +6515,7 @@
         <v>3562522</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6528,7 +6523,7 @@
         <v>3645922</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -6536,7 +6531,7 @@
         <v>2080000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -6544,7 +6539,7 @@
         <v>2216754</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6552,7 +6547,7 @@
         <v>593439</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6560,7 +6555,7 @@
         <v>704225</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
@@ -6568,7 +6563,7 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -6576,7 +6571,7 @@
         <v>4520000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -6584,7 +6579,7 @@
         <v>7390000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -6592,7 +6587,7 @@
         <v>9680000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4</v>
       </c>
@@ -6600,7 +6595,7 @@
         <v>11590000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>5</v>
       </c>
@@ -6608,7 +6603,7 @@
         <v>12980000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -6616,7 +6611,7 @@
         <v>13150000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7</v>
       </c>
@@ -6624,7 +6619,7 @@
         <v>13410000</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>8</v>
       </c>
@@ -6632,14 +6627,14 @@
         <v>13460000</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -6647,7 +6642,7 @@
         <v>4389983</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -6655,7 +6650,7 @@
         <v>2726781</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -6666,7 +6661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1</v>
       </c>
@@ -6677,7 +6672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2</v>
       </c>
@@ -6685,7 +6680,7 @@
         <v>2196354</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6693,7 +6688,7 @@
         <v>2781254</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>4</v>
       </c>
@@ -6701,7 +6696,7 @@
         <v>3221649</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>5</v>
       </c>
@@ -6709,7 +6704,7 @@
         <v>3610251</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>6</v>
       </c>
@@ -6717,7 +6712,7 @@
         <v>3789744</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>7</v>
       </c>
@@ -6725,7 +6720,7 @@
         <v>3675119</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>8</v>
       </c>
@@ -6733,19 +6728,19 @@
         <v>3496503</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>10000</v>
       </c>
@@ -6753,7 +6748,7 @@
         <v>2439024</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>100000</v>
       </c>
@@ -6761,7 +6756,7 @@
         <v>2409952</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1000000</v>
       </c>
@@ -6769,7 +6764,7 @@
         <v>2267573</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>10000000</v>
       </c>
@@ -6777,14 +6772,14 @@
         <v>2277613</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -6792,7 +6787,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1</v>
       </c>
@@ -6801,7 +6796,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2</v>
       </c>
@@ -6810,7 +6805,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>3</v>
       </c>
@@ -6819,10 +6814,10 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>11</v>
       </c>
@@ -6835,7 +6830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -6858,7 +6853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1</v>
       </c>
@@ -6869,7 +6864,7 @@
         <v>418939152.99515998</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>10</v>
       </c>
@@ -6880,7 +6875,7 @@
         <v>161098790.50095701</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>100</v>
       </c>
@@ -6891,7 +6886,7 @@
         <v>181994044.52139401</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1000</v>
       </c>
@@ -6902,7 +6897,7 @@
         <v>192417673.60928601</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>10000</v>
       </c>
@@ -6913,7 +6908,7 @@
         <v>185458998.17326799</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>100000</v>
       </c>
@@ -6936,7 +6931,7 @@
         <v>4.5978239059658102E-5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1000000</v>
       </c>
@@ -6947,7 +6942,7 @@
         <v>1.35229910329127E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>10000000</v>
       </c>
@@ -6958,7 +6953,7 @@
         <v>6.7647190708936802E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>17</v>
       </c>
@@ -6968,7 +6963,7 @@
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>18</v>
       </c>
@@ -6979,7 +6974,7 @@
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -6987,7 +6982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>9677000</v>
       </c>
@@ -6995,21 +6990,31 @@
         <v>11692164</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B75" s="6">
+        <v>12114171</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C84" s="2"/>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86" s="1"/>
     </row>
   </sheetData>
@@ -7033,7 +7038,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7042,7 +7047,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/preperation.xlsx
+++ b/results/preperation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t xml:space="preserve">Generator </t>
   </si>
@@ -83,6 +83,27 @@
   <si>
     <t>heighest</t>
   </si>
+  <si>
+    <t>v1</t>
+  </si>
+  <si>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>v3</t>
+  </si>
+  <si>
+    <t>v4</t>
+  </si>
+  <si>
+    <t>v5</t>
+  </si>
+  <si>
+    <t>Disco</t>
+  </si>
+  <si>
+    <t>Desis-Cen</t>
+  </si>
 </sst>
 </file>
 
@@ -123,16 +144,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -190,6 +213,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -452,6 +476,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -816,6 +841,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -965,6 +991,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1294,6 +1321,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1418,6 +1446,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1747,6 +1776,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1896,6 +1926,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2195,6 +2226,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2650,6 +2682,458 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Throughput</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$82:$A$89</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>v1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>v2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>v3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>v4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>v5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Scotty</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Disco</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Desis-Cen</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$82:$B$89</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1100000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4520000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11116783</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12114171</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18082706.766917199</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9398916</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2181646</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2801081</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-66F7-40F2-9262-4CC73ACF0766}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1385199424"/>
+        <c:axId val="1385200256"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1385199424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>system</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.50043284474571503"/>
+              <c:y val="0.87868037328667248"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1385200256"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1385200256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>tuples/sec</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.0421186981493301E-2"/>
+              <c:y val="0.38097623213764947"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1385199424"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2890,6 +3374,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -5460,6 +5984,509 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6116,16 +7143,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>48895</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>175895</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>130810</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>31115</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>346710</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6139,6 +7166,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6434,29 +7491,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H89"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="17.36328125" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6464,7 +7521,7 @@
         <v>1354279</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6475,7 +7532,7 @@
         <v>1176458</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6483,7 +7540,7 @@
         <v>2462051</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6491,7 +7548,7 @@
         <v>2769908</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6499,7 +7556,7 @@
         <v>3114585</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6507,7 +7564,7 @@
         <v>3468657</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6515,7 +7572,7 @@
         <v>3562522</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6523,7 +7580,7 @@
         <v>3645922</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -6531,7 +7588,7 @@
         <v>2080000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -6539,7 +7596,7 @@
         <v>2216754</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6547,7 +7604,7 @@
         <v>593439</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6555,15 +7612,15 @@
         <v>704225</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1</v>
       </c>
@@ -6571,7 +7628,7 @@
         <v>4520000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2</v>
       </c>
@@ -6579,7 +7636,7 @@
         <v>7390000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>3</v>
       </c>
@@ -6587,7 +7644,7 @@
         <v>9680000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>4</v>
       </c>
@@ -6595,7 +7652,7 @@
         <v>11590000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>5</v>
       </c>
@@ -6603,7 +7660,7 @@
         <v>12980000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>6</v>
       </c>
@@ -6611,7 +7668,7 @@
         <v>13150000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>7</v>
       </c>
@@ -6619,7 +7676,7 @@
         <v>13410000</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>8</v>
       </c>
@@ -6627,14 +7684,14 @@
         <v>13460000</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -6642,7 +7699,7 @@
         <v>4389983</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -6650,7 +7707,7 @@
         <v>2726781</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -6661,7 +7718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1</v>
       </c>
@@ -6672,7 +7729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2</v>
       </c>
@@ -6680,7 +7737,7 @@
         <v>2196354</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6688,7 +7745,7 @@
         <v>2781254</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>4</v>
       </c>
@@ -6696,7 +7753,7 @@
         <v>3221649</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>5</v>
       </c>
@@ -6704,7 +7761,7 @@
         <v>3610251</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>6</v>
       </c>
@@ -6712,7 +7769,7 @@
         <v>3789744</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>7</v>
       </c>
@@ -6720,7 +7777,7 @@
         <v>3675119</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>8</v>
       </c>
@@ -6728,19 +7785,19 @@
         <v>3496503</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>10000</v>
       </c>
@@ -6748,7 +7805,7 @@
         <v>2439024</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>100000</v>
       </c>
@@ -6756,7 +7813,7 @@
         <v>2409952</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1000000</v>
       </c>
@@ -6764,7 +7821,7 @@
         <v>2267573</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>10000000</v>
       </c>
@@ -6772,14 +7829,14 @@
         <v>2277613</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -6787,7 +7844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1</v>
       </c>
@@ -6796,7 +7853,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2</v>
       </c>
@@ -6805,7 +7862,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>3</v>
       </c>
@@ -6814,15 +7871,15 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
       <c r="D57" t="s">
         <v>15</v>
       </c>
@@ -6830,7 +7887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -6853,7 +7910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1</v>
       </c>
@@ -6864,7 +7921,7 @@
         <v>418939152.99515998</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>10</v>
       </c>
@@ -6875,7 +7932,7 @@
         <v>161098790.50095701</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>100</v>
       </c>
@@ -6886,7 +7943,7 @@
         <v>181994044.52139401</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1000</v>
       </c>
@@ -6897,7 +7954,7 @@
         <v>192417673.60928601</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>10000</v>
       </c>
@@ -6908,7 +7965,7 @@
         <v>185458998.17326799</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>100000</v>
       </c>
@@ -6931,7 +7988,7 @@
         <v>4.5978239059658102E-5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1000000</v>
       </c>
@@ -6942,7 +7999,7 @@
         <v>1.35229910329127E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>10000000</v>
       </c>
@@ -6953,28 +8010,28 @@
         <v>6.7647190708936802E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -6982,7 +8039,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>9677000</v>
       </c>
@@ -6990,32 +8047,87 @@
         <v>11692164</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B75" s="6">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B75" s="5">
         <v>12114171</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="8">
+        <v>1100000</v>
+      </c>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" s="8">
+        <v>4520000</v>
+      </c>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="8">
+        <v>11116783</v>
+      </c>
       <c r="C84" s="2"/>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B86" s="1"/>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" s="8">
+        <v>12114171</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86" s="8">
+        <v>18082706.766917199</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" s="8">
+        <v>9398916</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B88" s="8">
+        <v>2181646</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" s="8">
+        <v>2801081</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -7038,7 +8150,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7047,7 +8159,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/preperation.xlsx
+++ b/results/preperation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t xml:space="preserve">Generator </t>
   </si>
@@ -104,6 +104,9 @@
   <si>
     <t>Desis-Cen</t>
   </si>
+  <si>
+    <t>v6</t>
+  </si>
 </sst>
 </file>
 
@@ -118,7 +121,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,8 +134,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -140,11 +149,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -154,8 +178,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -213,7 +244,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -476,7 +506,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -841,7 +870,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -991,7 +1019,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1321,7 +1348,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1446,7 +1472,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1776,7 +1801,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1926,7 +1950,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2226,7 +2249,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2774,9 +2796,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$82:$A$89</c:f>
+              <c:f>Sheet1!$A$82:$A$90</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>v1</c:v>
                 </c:pt>
@@ -2793,12 +2815,15 @@
                   <c:v>v5</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>v6</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Scotty</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>Disco</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>Desis-Cen</c:v>
                 </c:pt>
               </c:strCache>
@@ -2806,10 +2831,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$82:$B$89</c:f>
+              <c:f>Sheet1!$B$82:$B$90</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1100000</c:v>
                 </c:pt>
@@ -2826,12 +2851,15 @@
                   <c:v>18082706.766917199</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>30545075.399999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>9398916</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>2181646</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>2801081</c:v>
                 </c:pt>
               </c:numCache>
@@ -7491,7 +7519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
@@ -8107,27 +8135,39 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B87" s="8">
-        <v>9398916</v>
+        <v>29</v>
+      </c>
+      <c r="B87" s="9">
+        <v>30545075.399999999</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B88" s="8">
-        <v>2181646</v>
+        <v>9398916</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" s="8">
+        <v>2181646</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B90" s="8">
         <v>2801081</v>
       </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="9">
